--- a/artfynd/A 25952-2025 artfynd.xlsx
+++ b/artfynd/A 25952-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89604311</v>
+        <v>89604310</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456601.8184327521</v>
+        <v>456647</v>
       </c>
       <c r="R2" t="n">
-        <v>7091234.064450738</v>
+        <v>7091223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89604310</v>
+        <v>89604311</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456647.0136980348</v>
+        <v>456602</v>
       </c>
       <c r="R3" t="n">
-        <v>7091222.883807757</v>
+        <v>7091234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
